--- a/public/upload/export_excel/ข้อมูลยานพาหนะ-สาขาเจริญใจ07-2025.xlsx
+++ b/public/upload/export_excel/ข้อมูลยานพาหนะ-สาขาเจริญใจ07-2025.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="14">
   <si>
     <t>ข้อมูลยานพาหนะ สาขาเจริญใจ</t>
   </si>
@@ -39,6 +39,24 @@
   </si>
   <si>
     <t>หมายเหตุ</t>
+  </si>
+  <si>
+    <t>13/06/2025</t>
+  </si>
+  <si>
+    <t>A102</t>
+  </si>
+  <si>
+    <t>บริษัท ธนพล วรินทร</t>
+  </si>
+  <si>
+    <t>รถยนต์</t>
+  </si>
+  <si>
+    <t>we123</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -381,7 +399,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -427,6 +445,27 @@
         <v>7</v>
       </c>
     </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/upload/export_excel/ข้อมูลยานพาหนะ-สาขาเจริญใจ07-2025.xlsx
+++ b/public/upload/export_excel/ข้อมูลยานพาหนะ-สาขาเจริญใจ07-2025.xlsx
@@ -15,9 +15,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="14">
-  <si>
-    <t>ข้อมูลยานพาหนะ สาขาเจริญใจ</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="21">
+  <si>
+    <t xml:space="preserve">ข้อมูลยานพาหนะ </t>
   </si>
   <si>
     <t>วันที่เพิ่มข้อมูล</t>
@@ -41,7 +41,7 @@
     <t>หมายเหตุ</t>
   </si>
   <si>
-    <t>13/06/2025</t>
+    <t>11/08/2025</t>
   </si>
   <si>
     <t>A102</t>
@@ -50,13 +50,34 @@
     <t>บริษัท ธนพล วรินทร</t>
   </si>
   <si>
+    <t>รถจักรยานยนต์</t>
+  </si>
+  <si>
+    <t>we123</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>456 มท</t>
+  </si>
+  <si>
+    <t>14/08/2025</t>
+  </si>
+  <si>
+    <t>บริษัท ภัทรพล สุภาพร</t>
+  </si>
+  <si>
+    <t>qw</t>
+  </si>
+  <si>
+    <t>wer</t>
+  </si>
+  <si>
     <t>รถยนต์</t>
-  </si>
-  <si>
-    <t>we123</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -95,11 +116,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -399,71 +417,219 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1" t="s">
+      <c r="F4" t="s">
         <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6">
+        <v>123</v>
+      </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <v>456</v>
+      </c>
+      <c r="G7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10">
+        <v>123</v>
+      </c>
+      <c r="G10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11">
+        <v>456</v>
+      </c>
+      <c r="G11" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
